--- a/artfynd/A 59493-2025 artfynd.xlsx
+++ b/artfynd/A 59493-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136206180</v>
       </c>
       <c r="B2" t="n">
-        <v>96927</v>
+        <v>96930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136206175</v>
       </c>
       <c r="B3" t="n">
-        <v>96567</v>
+        <v>96570</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 59493-2025 artfynd.xlsx
+++ b/artfynd/A 59493-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136206180</v>
       </c>
       <c r="B2" t="n">
-        <v>96930</v>
+        <v>96931</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136206175</v>
       </c>
       <c r="B3" t="n">
-        <v>96570</v>
+        <v>96571</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 59493-2025 artfynd.xlsx
+++ b/artfynd/A 59493-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136206180</v>
       </c>
       <c r="B2" t="n">
-        <v>96931</v>
+        <v>96936</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136206175</v>
       </c>
       <c r="B3" t="n">
-        <v>96571</v>
+        <v>96576</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136206169</v>
       </c>
       <c r="B4" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136206190</v>
       </c>
       <c r="B5" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>136206196</v>
       </c>
       <c r="B6" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136206182</v>
       </c>
       <c r="B7" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>136206170</v>
       </c>
       <c r="B8" t="n">
-        <v>58162</v>
+        <v>58164</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>136206177</v>
       </c>
       <c r="B9" t="n">
-        <v>58162</v>
+        <v>58164</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>136206183</v>
       </c>
       <c r="B10" t="n">
-        <v>58162</v>
+        <v>58164</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>136206172</v>
       </c>
       <c r="B11" t="n">
-        <v>58868</v>
+        <v>58870</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>136206197</v>
       </c>
       <c r="B12" t="n">
-        <v>56927</v>
+        <v>56929</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 59493-2025 artfynd.xlsx
+++ b/artfynd/A 59493-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136206180</v>
       </c>
       <c r="B2" t="n">
-        <v>96936</v>
+        <v>96938</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136206175</v>
       </c>
       <c r="B3" t="n">
-        <v>96576</v>
+        <v>96578</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
